--- a/factory/工厂配送麦安研+焙满香门店商品周度销售对比表_格式化模板.xlsx
+++ b/factory/工厂配送麦安研+焙满香门店商品周度销售对比表_格式化模板.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0830496-726A-43FF-8111-60BB7862B8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0B4481-E0F1-4961-A5A7-DD01A10FD964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="货品对比表6.8-6.14" sheetId="1" r:id="rId1"/>
-    <sheet name="货品销售排行表6.8-6.14" sheetId="4" r:id="rId2"/>
-    <sheet name="配送杏坛店产品销售排行表" sheetId="5" r:id="rId3"/>
+    <sheet name="商品对比表6.8-6.14" sheetId="1" r:id="rId1"/>
+    <sheet name="商品销售排行表6.8-6.14" sheetId="4" r:id="rId2"/>
+    <sheet name="配送杏坛店商品销售排行表" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -75,11 +75,16 @@
     <t>合计</t>
   </si>
   <si>
-    <t>2026年6月8日至6月14日工厂配送麦安研杏坛门店货品销售排行表</t>
+    <t>杏坛数量</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026年6月8日至6月14日工厂配送麦安研杏坛门店商品销售排行表</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>2026年6月8日至6月14日工厂配送麦安研门店货品对比表及各类别产品销售排行</t>
+      <t>2026年6月8日至6月14日工厂配送麦安研+焙满香门店商品对比表及各类别产品销售排行</t>
     </r>
     <r>
       <rPr>
@@ -92,14 +97,11 @@
       </rPr>
       <t>(近期新品用红色标识)</t>
     </r>
-  </si>
-  <si>
-    <t>杏坛数量</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>2026年6月8日至6月14日工厂配送麦安研门店货品销售排行</t>
+      <t>2026年6月8日至6月14日工厂配送麦安研+焙满香门店商品销售排行</t>
     </r>
     <r>
       <rPr>
@@ -112,6 +114,7 @@
       </rPr>
       <t>（近期新品用红色标识）</t>
     </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -848,7 +851,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -892,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>9</v>
@@ -1225,7 +1228,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
